--- a/Result/profitability/5310.xlsx
+++ b/Result/profitability/5310.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.35375</v>
+        <v>0.335</v>
       </c>
       <c r="N2" t="n">
-        <v>12.81875</v>
+        <v>12.5</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0675</v>
+        <v>0.37875</v>
       </c>
       <c r="N3" t="n">
-        <v>17.32625</v>
+        <v>17.36625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1225</v>
+        <v>0.31875</v>
       </c>
       <c r="N4" t="n">
-        <v>19.96875</v>
+        <v>19.43375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02250000000000001</v>
+        <v>0.26625</v>
       </c>
       <c r="N5" t="n">
-        <v>21.4075</v>
+        <v>20.83875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.21</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01999999999999999</v>
+        <v>0.19625</v>
       </c>
       <c r="N6" t="n">
-        <v>24.06125</v>
+        <v>24.3325</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.46</v>
       </c>
       <c r="M7" t="n">
-        <v>0.24375</v>
+        <v>0.5625</v>
       </c>
       <c r="N7" t="n">
-        <v>26.68375</v>
+        <v>26.29875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.74</v>
       </c>
       <c r="M8" t="n">
-        <v>0.52</v>
+        <v>0.7725</v>
       </c>
       <c r="N8" t="n">
-        <v>31.3875</v>
+        <v>31.27125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.22</v>
       </c>
       <c r="M9" t="n">
-        <v>0.54</v>
+        <v>0.5399999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>32.9475</v>
@@ -1645,7 +1645,7 @@
         <v>-0.16</v>
       </c>
       <c r="M10" t="n">
-        <v>0.46625</v>
+        <v>0.4662499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>33.185</v>
@@ -1772,7 +1772,7 @@
         <v>0.21</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>30.5775</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5310</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3764.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>68</v>
+      </c>
+      <c r="J75" t="n">
+        <v>60</v>
+      </c>
+      <c r="K75" t="n">
+        <v>60</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.1625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>33.66666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9299999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0887404580152672</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.549999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3226950354609929</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
